--- a/raw_data_source/PwC_raw_scrapped_data.xlsx
+++ b/raw_data_source/PwC_raw_scrapped_data.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10512"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="pdf_links_with_content" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="pdf_links_with_content"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -5784,29 +5778,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="165" formatCode="m/d/yy"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF0000ff"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5817,7 +5813,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -5829,38 +5832,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="8">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -5887,22 +5904,82 @@
         <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -5914,131 +5991,158 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -6051,27 +6155,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="117.44140625" customWidth="1"/>
-    <col min="2" max="2" width="80.109375" customWidth="1"/>
-    <col min="3" max="3" width="54.44140625" customWidth="1"/>
-    <col min="4" max="4" width="68.77734375" customWidth="1"/>
-    <col min="5" max="5" width="67.44140625" customWidth="1"/>
-    <col min="6" max="6" width="81.21875" customWidth="1"/>
+    <col min="1" max="1" style="6" width="117.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="80.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="54.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="68.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="67.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="81.29071428571429" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -6084,14 +6188,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="3996">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>45842</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -6104,14 +6208,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="940.5">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>45720</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -6124,14 +6228,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -6144,14 +6248,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="3847.5">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -6164,14 +6268,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="2115">
+      <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>45964</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -6184,14 +6288,14 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>45933</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -6200,15 +6304,16 @@
       <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>45841</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -6217,15 +6322,16 @@
       <c r="E8" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>45780</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -6234,15 +6340,16 @@
       <c r="E9" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="5397.75">
+      <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>45750</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -6255,14 +6362,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>45750</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -6271,15 +6378,16 @@
       <c r="E11" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -6288,15 +6396,16 @@
       <c r="E12" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="747">
+      <c r="A13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -6309,14 +6418,14 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -6325,15 +6434,16 @@
       <c r="E14" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -6346,14 +6456,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -6366,14 +6476,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -6386,14 +6496,14 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -6406,14 +6516,14 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -6426,14 +6536,14 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -6446,14 +6556,14 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>45931</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -6466,14 +6576,14 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>111</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -6486,14 +6596,14 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -6506,14 +6616,14 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -6522,15 +6632,16 @@
       <c r="E24" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <v>45608</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -6544,56 +6655,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="B2" r:id="rId2"/>
-    <hyperlink ref="A3" r:id="rId3"/>
-    <hyperlink ref="B3" r:id="rId4"/>
-    <hyperlink ref="A4" r:id="rId5"/>
-    <hyperlink ref="B4" r:id="rId6"/>
-    <hyperlink ref="A5" r:id="rId7"/>
-    <hyperlink ref="B5" r:id="rId8"/>
-    <hyperlink ref="A6" r:id="rId9"/>
-    <hyperlink ref="B6" r:id="rId10"/>
-    <hyperlink ref="A7" r:id="rId11"/>
-    <hyperlink ref="B7" r:id="rId12"/>
-    <hyperlink ref="A8" r:id="rId13"/>
-    <hyperlink ref="B8" r:id="rId14"/>
-    <hyperlink ref="A9" r:id="rId15"/>
-    <hyperlink ref="B9" r:id="rId16"/>
-    <hyperlink ref="A10" r:id="rId17"/>
-    <hyperlink ref="B10" r:id="rId18"/>
-    <hyperlink ref="A11" r:id="rId19"/>
-    <hyperlink ref="B11" r:id="rId20"/>
-    <hyperlink ref="A12" r:id="rId21"/>
-    <hyperlink ref="B12" r:id="rId22"/>
-    <hyperlink ref="A13" r:id="rId23"/>
-    <hyperlink ref="B13" r:id="rId24"/>
-    <hyperlink ref="A14" r:id="rId25"/>
-    <hyperlink ref="B14" r:id="rId26"/>
-    <hyperlink ref="A15" r:id="rId27"/>
-    <hyperlink ref="B15" r:id="rId28"/>
-    <hyperlink ref="A16" r:id="rId29"/>
-    <hyperlink ref="B16" r:id="rId30"/>
-    <hyperlink ref="A17" r:id="rId31"/>
-    <hyperlink ref="B17" r:id="rId32"/>
-    <hyperlink ref="A18" r:id="rId33"/>
-    <hyperlink ref="B18" r:id="rId34"/>
-    <hyperlink ref="A19" r:id="rId35"/>
-    <hyperlink ref="B19" r:id="rId36"/>
-    <hyperlink ref="A20" r:id="rId37"/>
-    <hyperlink ref="B20" r:id="rId38"/>
-    <hyperlink ref="A21" r:id="rId39"/>
-    <hyperlink ref="B21" r:id="rId40"/>
-    <hyperlink ref="A22" r:id="rId41"/>
-    <hyperlink ref="B22" r:id="rId42"/>
-    <hyperlink ref="A23" r:id="rId43"/>
-    <hyperlink ref="B23" r:id="rId44"/>
-    <hyperlink ref="A24" r:id="rId45"/>
-    <hyperlink ref="B24" r:id="rId46"/>
-    <hyperlink ref="A25" r:id="rId47"/>
-    <hyperlink ref="B25" r:id="rId48"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>